--- a/backend/data/financials_by_company/0348.HK.xlsx
+++ b/backend/data/financials_by_company/0348.HK.xlsx
@@ -4020,7 +4020,7 @@
         <v>-2606000</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>0</v>
       </c>
       <c r="EB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0.016599998</v>
